--- a/Inputs_July.xlsx
+++ b/Inputs_July.xlsx
@@ -24741,7 +24741,7 @@
     <row r="86">
       <c r="B86" s="63" t="inlineStr">
         <is>
-          <t>DC804800R</t>
+          <t>DC804600R</t>
         </is>
       </c>
       <c r="C86" s="69" t="n">
